--- a/backend/{templates}/fuel-financial-inputs.xlsx
+++ b/backend/{templates}/fuel-financial-inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:3_{297C9F4D-5BEC-4077-8986-513ACDF59508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20D538B3-3C13-4820-BDE1-34A1EF4D45E7}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:3_{297C9F4D-5BEC-4077-8986-513ACDF59508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F161B70-FCC9-4177-A295-25DFDA84BFBC}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" r:id="rId1"/>
@@ -216,6 +216,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/backend/{templates}/fuel-financial-inputs.xlsx
+++ b/backend/{templates}/fuel-financial-inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:3_{297C9F4D-5BEC-4077-8986-513ACDF59508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F161B70-FCC9-4177-A295-25DFDA84BFBC}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:3_{297C9F4D-5BEC-4077-8986-513ACDF59508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0F7028D-8375-4DBD-8F8A-EC3B86D466EA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="16">
   <si>
     <t>Inputs</t>
   </si>
@@ -540,13 +540,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -557,130 +557,127 @@
         <v>2</v>
       </c>
       <c r="D1" s="3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E1" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F1" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G1" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J1" s="3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K1" s="3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L1" s="3">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M1" s="3">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N1" s="3">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O1" s="3">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P1" s="3">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q1" s="3">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R1" s="3">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S1" s="3">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T1" s="3">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U1" s="3">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V1" s="3">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W1" s="3">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X1" s="3">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y1" s="3">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z1" s="3">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA1" s="3">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB1" s="3">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC1" s="3">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD1" s="3">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE1" s="3">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF1" s="3">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG1" s="3">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH1" s="3">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI1" s="3">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ1" s="3">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK1" s="3">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL1" s="3">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM1" s="3">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN1" s="3">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO1" s="3">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP1" s="3">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ1" s="3">
-        <v>2059</v>
-      </c>
-      <c r="AR1" s="3">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -810,11 +807,8 @@
       <c r="AQ2" s="6">
         <v>0</v>
       </c>
-      <c r="AR2" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -944,11 +938,8 @@
       <c r="AQ3" s="6">
         <v>0</v>
       </c>
-      <c r="AR3" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1078,11 +1069,8 @@
       <c r="AQ4" s="6">
         <v>0</v>
       </c>
-      <c r="AR4" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -1210,9 +1198,6 @@
         <v>0</v>
       </c>
       <c r="AQ5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1225,13 +1210,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1242,130 +1227,127 @@
         <v>2</v>
       </c>
       <c r="D1" s="3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E1" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F1" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G1" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J1" s="3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K1" s="3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L1" s="3">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M1" s="3">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N1" s="3">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O1" s="3">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P1" s="3">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q1" s="3">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R1" s="3">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S1" s="3">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T1" s="3">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U1" s="3">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V1" s="3">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W1" s="3">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X1" s="3">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y1" s="3">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z1" s="3">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA1" s="3">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB1" s="3">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC1" s="3">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD1" s="3">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE1" s="3">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF1" s="3">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG1" s="3">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH1" s="3">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI1" s="3">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ1" s="3">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK1" s="3">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL1" s="3">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM1" s="3">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN1" s="3">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO1" s="3">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP1" s="3">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ1" s="3">
-        <v>2059</v>
-      </c>
-      <c r="AR1" s="3">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1495,11 +1477,8 @@
       <c r="AQ2" s="6">
         <v>0</v>
       </c>
-      <c r="AR2" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1629,11 +1608,8 @@
       <c r="AQ3" s="6">
         <v>0</v>
       </c>
-      <c r="AR3" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1763,11 +1739,8 @@
       <c r="AQ4" s="6">
         <v>0</v>
       </c>
-      <c r="AR4" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -1895,9 +1868,6 @@
         <v>0</v>
       </c>
       <c r="AQ5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1910,13 +1880,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916D2B2D-4AA6-4AEC-A74D-5F74F284844E}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1927,130 +1897,127 @@
         <v>2</v>
       </c>
       <c r="D1" s="3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E1" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F1" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G1" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J1" s="3">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K1" s="3">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L1" s="3">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M1" s="3">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N1" s="3">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O1" s="3">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P1" s="3">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q1" s="3">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R1" s="3">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S1" s="3">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T1" s="3">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U1" s="3">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V1" s="3">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W1" s="3">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X1" s="3">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y1" s="3">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z1" s="3">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA1" s="3">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB1" s="3">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC1" s="3">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD1" s="3">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE1" s="3">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF1" s="3">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG1" s="3">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH1" s="3">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI1" s="3">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ1" s="3">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK1" s="3">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL1" s="3">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM1" s="3">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN1" s="3">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO1" s="3">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP1" s="3">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ1" s="3">
-        <v>2059</v>
-      </c>
-      <c r="AR1" s="3">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -2180,11 +2147,8 @@
       <c r="AQ2" s="6">
         <v>0</v>
       </c>
-      <c r="AR2" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2314,11 +2278,8 @@
       <c r="AQ3" s="6">
         <v>0</v>
       </c>
-      <c r="AR3" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -2448,11 +2409,8 @@
       <c r="AQ4" s="6">
         <v>0</v>
       </c>
-      <c r="AR4" s="6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -2580,9 +2538,6 @@
         <v>15</v>
       </c>
       <c r="AQ5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR5" s="7" t="s">
         <v>15</v>
       </c>
     </row>
